--- a/document/ログイン機能_テスト仕様兼結果報告書.xlsx
+++ b/document/ログイン機能_テスト仕様兼結果報告書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A597A41-AED0-4801-BA9A-A5EF451A043A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4F1D93-20A3-42AA-966E-87F22F8997B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様書兼結果報告書" sheetId="1" r:id="rId1"/>
@@ -211,13 +211,6 @@
 未ログイン状態では menu.jsp を直接表示できない</t>
   </si>
   <si>
-    <t>m_userに以下が登録済み
-user_id：admin
-password：admin
-user_name：test</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>menu.jspへ遷移する
 セッションに userName「アドミン太郎」が保持される</t>
     <rPh sb="34" eb="36">
@@ -263,6 +256,16 @@
     <t>林</t>
     <rPh sb="0" eb="1">
       <t>ハヤシ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>m_userに以下が登録済み
+user_id：admin
+password：admin
+user_name：アドミン太郎</t>
+    <rPh sb="58" eb="60">
+      <t>タロウ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
@@ -880,6 +883,111 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -897,111 +1005,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1181,188 +1184,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="47" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="47" t="s">
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="47" t="s">
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="47" t="s">
+      <c r="P1" s="38"/>
+      <c r="Q1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="49"/>
-      <c r="S1" s="47" t="s">
+      <c r="R1" s="38"/>
+      <c r="S1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="50"/>
+      <c r="T1" s="39"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="51" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="51" t="s">
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="51" t="s">
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="56"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="45"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="57"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="46"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="58"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="47"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="60" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="50"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="39"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="37"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="24"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="37"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="24"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="9"/>
@@ -1561,37 +1564,37 @@
       <c r="T14" s="11"/>
     </row>
     <row r="15" spans="1:26" ht="27" customHeight="1">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="51"/>
+      <c r="C15" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="31" t="s">
+      <c r="D15" s="51"/>
+      <c r="E15" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="31" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="31" t="s">
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="31" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="31" t="s">
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
       <c r="R15" s="8" t="s">
         <v>23</v>
       </c>
@@ -1603,43 +1606,43 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A16" s="27">
+      <c r="A16" s="52">
         <f>ROW()-15</f>
         <v>1</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="53"/>
+      <c r="C16" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="27" t="s">
+      <c r="D16" s="53"/>
+      <c r="E16" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29" t="s">
+      <c r="F16" s="53"/>
+      <c r="G16" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29" t="s">
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="K16" s="28"/>
-      <c r="L16" s="30" t="s">
+      <c r="K16" s="53"/>
+      <c r="L16" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="30" t="s">
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="61">
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="21">
         <v>46176</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T16" s="7"/>
       <c r="U16" s="3"/>
@@ -1649,43 +1652,43 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="81" customHeight="1">
-      <c r="A17" s="27">
+    <row r="17" spans="1:26" ht="111.75" customHeight="1">
+      <c r="A17" s="52">
         <v>2</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="27" t="s">
+      <c r="B17" s="53"/>
+      <c r="C17" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27" t="s">
+      <c r="D17" s="53"/>
+      <c r="E17" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29" t="s">
+      <c r="F17" s="53"/>
+      <c r="G17" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29" t="s">
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" s="53"/>
+      <c r="L17" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="28"/>
-      <c r="L17" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="M17" s="28"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="61">
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="21">
         <v>46176</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T17" s="7"/>
       <c r="U17" s="3"/>
@@ -1696,42 +1699,42 @@
       <c r="Z17" s="3"/>
     </row>
     <row r="18" spans="1:26" ht="108" customHeight="1">
-      <c r="A18" s="27">
+      <c r="A18" s="52">
         <v>3</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="53"/>
+      <c r="C18" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="27" t="s">
+      <c r="D18" s="53"/>
+      <c r="E18" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29" t="s">
+      <c r="F18" s="53"/>
+      <c r="G18" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="29" t="s">
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="28"/>
-      <c r="L18" s="30" t="s">
+      <c r="K18" s="53"/>
+      <c r="L18" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="21">
+        <v>46176</v>
+      </c>
+      <c r="S18" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="61">
-        <v>46176</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="T18" s="7"/>
       <c r="U18" s="3"/>
@@ -1742,42 +1745,42 @@
       <c r="Z18" s="3"/>
     </row>
     <row r="19" spans="1:26" ht="111.75" customHeight="1">
-      <c r="A19" s="27">
+      <c r="A19" s="52">
         <v>4</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="53"/>
+      <c r="C19" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="27" t="s">
+      <c r="D19" s="53"/>
+      <c r="E19" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29" t="s">
+      <c r="F19" s="53"/>
+      <c r="G19" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="29" t="s">
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="53"/>
+      <c r="L19" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="K19" s="28"/>
-      <c r="L19" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="30" t="s">
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="61">
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="21">
         <v>46176</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T19" s="7"/>
       <c r="U19" s="3"/>
@@ -1788,42 +1791,42 @@
       <c r="Z19" s="3"/>
     </row>
     <row r="20" spans="1:26" ht="72.75" customHeight="1">
-      <c r="A20" s="27">
+      <c r="A20" s="52">
         <v>5</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="27" t="s">
+      <c r="B20" s="53"/>
+      <c r="C20" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="27" t="s">
+      <c r="D20" s="53"/>
+      <c r="E20" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29" t="s">
+      <c r="F20" s="53"/>
+      <c r="G20" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="29" t="s">
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="28"/>
-      <c r="L20" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="30" t="s">
+      <c r="K20" s="53"/>
+      <c r="L20" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="61">
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="21">
         <v>46176</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T20" s="7"/>
       <c r="U20" s="3"/>
@@ -1834,42 +1837,42 @@
       <c r="Z20" s="3"/>
     </row>
     <row r="21" spans="1:26" ht="84" customHeight="1">
-      <c r="A21" s="27">
+      <c r="A21" s="52">
         <v>6</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="27" t="s">
+      <c r="B21" s="53"/>
+      <c r="C21" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="27" t="s">
+      <c r="D21" s="53"/>
+      <c r="E21" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="29" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="29" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="28"/>
-      <c r="L21" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="30" t="s">
+      <c r="K21" s="53"/>
+      <c r="L21" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="61">
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="21">
         <v>46176</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T21" s="7"/>
       <c r="U21" s="3"/>
@@ -1880,42 +1883,42 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A22" s="27">
+      <c r="A22" s="52">
         <v>7</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="27" t="s">
+      <c r="B22" s="53"/>
+      <c r="C22" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="27" t="s">
+      <c r="D22" s="53"/>
+      <c r="E22" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29" t="s">
+      <c r="F22" s="53"/>
+      <c r="G22" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29" t="s">
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K22" s="28"/>
-      <c r="L22" s="30" t="s">
+      <c r="K22" s="53"/>
+      <c r="L22" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="30" t="s">
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="61">
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="21">
         <v>46176</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T22" s="7"/>
       <c r="U22" s="3"/>
@@ -1926,42 +1929,42 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="1:26" ht="95.25" customHeight="1">
-      <c r="A23" s="27">
+      <c r="A23" s="52">
         <v>11</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="27" t="s">
+      <c r="B23" s="53"/>
+      <c r="C23" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="27" t="s">
+      <c r="D23" s="53"/>
+      <c r="E23" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="28"/>
-      <c r="G23" s="29" t="s">
+      <c r="F23" s="53"/>
+      <c r="G23" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="29" t="s">
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="K23" s="28"/>
-      <c r="L23" s="30" t="s">
+      <c r="K23" s="53"/>
+      <c r="L23" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="30" t="s">
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="61">
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="21">
         <v>46176</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T23" s="7"/>
       <c r="U23" s="3"/>
@@ -1972,23 +1975,23 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="24"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="23"/>
+      <c r="A24" s="59"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="58"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="5"/>
@@ -2986,6 +2989,77 @@
     <row r="993" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="87">
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="G6:T6"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="G7:T7"/>
@@ -3002,77 +3076,6 @@
     <mergeCell ref="S2:T4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
